--- a/Analysed/Gemini_gemini-3-flash-preview_naive.xlsx
+++ b/Analysed/Gemini_gemini-3-flash-preview_naive.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H2" t="n">
-        <v>1.547826086956522</v>
+        <v>1.54312693498452</v>
       </c>
       <c r="I2" t="n">
-        <v>1.802794759283313</v>
+        <v>1.800002665976698</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09345794392523364</v>
+        <v>0.09627329192546584</v>
       </c>
     </row>
     <row r="3">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
-        <v>1.463761467889908</v>
+        <v>1.426964285714286</v>
       </c>
       <c r="I4" t="n">
-        <v>1.761959136870092</v>
+        <v>1.738263706773433</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1574074074074074</v>
+        <v>0.1801801801801802</v>
       </c>
     </row>
     <row r="5">
@@ -693,10 +693,10 @@
         <v>51</v>
       </c>
       <c r="H6" t="n">
-        <v>3.289607843137254</v>
+        <v>3.291764705882353</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4918709519537</v>
+        <v>3.494806791484177</v>
       </c>
       <c r="J6" t="n">
         <v>0.38</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6892</v>
+        <v>2.803506493506494</v>
       </c>
       <c r="I11" t="n">
-        <v>3.515807541186899</v>
+        <v>3.653158924803318</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3648648648648649</v>
+        <v>0.3552631578947368</v>
       </c>
     </row>
     <row r="12">
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>4.118213166144201</v>
+        <v>4.102118380062305</v>
       </c>
       <c r="I14" t="n">
-        <v>4.71243519367062</v>
+        <v>4.699294438987523</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6509433962264151</v>
+        <v>0.646875</v>
       </c>
     </row>
     <row r="15">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.4376315789473684</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5972459315078694</v>
+        <v>0.5897122402628162</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5945945945945946</v>
       </c>
     </row>
     <row r="20">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H26" t="n">
-        <v>19.57754098360655</v>
+        <v>19.55047999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>19.59487667231613</v>
+        <v>19.5681841569421</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2231404958677686</v>
+        <v>0.2419354838709677</v>
       </c>
     </row>
     <row r="27">
@@ -1746,16 +1746,16 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H30" t="n">
-        <v>23.29390243902439</v>
+        <v>22.975</v>
       </c>
       <c r="I30" t="n">
-        <v>24.01456026826327</v>
+        <v>23.77607505956555</v>
       </c>
       <c r="J30" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
     </row>
     <row r="31">
@@ -1834,16 +1834,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H32" t="n">
-        <v>31.54169491525424</v>
+        <v>31.60512396694216</v>
       </c>
       <c r="I32" t="n">
-        <v>31.58554504725545</v>
+        <v>31.65030197132459</v>
       </c>
       <c r="J32" t="n">
-        <v>0.188034188034188</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H33" t="n">
-        <v>14.48030303030303</v>
+        <v>14.62428571428571</v>
       </c>
       <c r="I33" t="n">
-        <v>14.58800565844794</v>
+        <v>14.73647273167594</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2753623188405797</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H37" t="n">
-        <v>41.51052631578947</v>
+        <v>43.01612903225809</v>
       </c>
       <c r="I37" t="n">
-        <v>41.56461678424393</v>
+        <v>43.0897974602027</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38">
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H40" t="n">
-        <v>41.92148148148147</v>
+        <v>42.3901818181818</v>
       </c>
       <c r="I40" t="n">
-        <v>50.31132727181674</v>
+        <v>50.68188509086492</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1775700934579439</v>
+        <v>0.1743119266055046</v>
       </c>
     </row>
     <row r="41">
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H41" t="n">
-        <v>28.01923076923076</v>
+        <v>28.01625</v>
       </c>
       <c r="I41" t="n">
-        <v>36.26907455713158</v>
+        <v>36.0959814245298</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1558441558441558</v>
+        <v>0.1518987341772152</v>
       </c>
     </row>
     <row r="42">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H42" t="n">
-        <v>96.90000000000002</v>
+        <v>99.7177777777778</v>
       </c>
       <c r="I42" t="n">
-        <v>108.6120321828283</v>
+        <v>111.419611479408</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H43" t="n">
-        <v>44.9375</v>
+        <v>43.39558823529412</v>
       </c>
       <c r="I43" t="n">
-        <v>50.11522719122973</v>
+        <v>47.95391411982722</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3703703703703703</v>
+        <v>0.4848484848484849</v>
       </c>
     </row>
     <row r="44">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H44" t="n">
-        <v>19.67314814814815</v>
+        <v>19.65107692307692</v>
       </c>
       <c r="I44" t="n">
-        <v>20.21126528558874</v>
+        <v>20.19205549791227</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07739938080495357</v>
+        <v>0.08024691358024691</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>115</v>
+        <v>206</v>
       </c>
       <c r="H45" t="n">
-        <v>18.09826086956522</v>
+        <v>44.36189320388349</v>
       </c>
       <c r="I45" t="n">
-        <v>18.8025797952441</v>
+        <v>44.62044986456888</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1317073170731707</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="H46" t="n">
-        <v>20.88764705882353</v>
+        <v>18.09826086956522</v>
       </c>
       <c r="I46" t="n">
-        <v>21.5569589419178</v>
+        <v>18.8025797952441</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.2105263157894737</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H47" t="n">
-        <v>11.71109090909091</v>
+        <v>20.88764705882353</v>
       </c>
       <c r="I47" t="n">
-        <v>13.17623570192668</v>
+        <v>21.5569589419178</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4259259259259259</v>
+        <v>0.2619047619047619</v>
       </c>
     </row>
     <row r="48">
@@ -2534,20 +2534,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H48" t="n">
-        <v>14.54375</v>
+        <v>11.71109090909091</v>
       </c>
       <c r="I48" t="n">
-        <v>15.99896738855355</v>
+        <v>13.17623570192668</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4259259259259259</v>
       </c>
     </row>
     <row r="49">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>315</v>
+        <v>40</v>
       </c>
       <c r="H49" t="n">
-        <v>26.47380952380952</v>
+        <v>14.54375</v>
       </c>
       <c r="I49" t="n">
-        <v>27.98442075087324</v>
+        <v>15.99896738855355</v>
       </c>
       <c r="J49" t="n">
-        <v>0.04458598726114649</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="H50" t="n">
-        <v>19.50181347150259</v>
+        <v>26.47380952380952</v>
       </c>
       <c r="I50" t="n">
-        <v>21.58752826712539</v>
+        <v>27.98442075087324</v>
       </c>
       <c r="J50" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.04458598726114649</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="H51" t="n">
-        <v>24.31714285714285</v>
+        <v>19.66076923076923</v>
       </c>
       <c r="I51" t="n">
-        <v>26.21254915748053</v>
+        <v>21.76708002513228</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.06701030927835051</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="H52" t="n">
-        <v>23.96789473684211</v>
+        <v>24.31714285714285</v>
       </c>
       <c r="I52" t="n">
-        <v>26.7662265098939</v>
+        <v>26.21254915748053</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.1346153846153846</v>
       </c>
     </row>
     <row r="53">
@@ -2754,17 +2754,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H53" t="n">
-        <v>14.63260869565218</v>
+        <v>23.96789473684211</v>
       </c>
       <c r="I53" t="n">
-        <v>14.964403414945</v>
+        <v>26.7662265098939</v>
       </c>
       <c r="J53" t="n">
         <v>0.8666666666666667</v>
@@ -2798,19 +2798,63 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" t="n">
+        <v>14.63260869565218</v>
+      </c>
+      <c r="I54" t="n">
+        <v>14.964403414945</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gemini-3-flash-preview</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>34</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>15.01352941176471</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>16.76498469324401</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>0.8484848484848485</v>
       </c>
     </row>
@@ -2857,14 +2901,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.3739</v>
+        <v>17.9347</v>
       </c>
       <c r="C2" t="n">
-        <v>17.0128</v>
+        <v>17.4993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.3739 ± 17.0128</t>
+          <t>17.9347 ± 17.4993</t>
         </is>
       </c>
     </row>
@@ -2875,14 +2919,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.5593</v>
+        <v>19.0895</v>
       </c>
       <c r="C3" t="n">
-        <v>18.6453</v>
+        <v>19.0381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.5593 ± 18.6453</t>
+          <t>19.0895 ± 19.0381</t>
         </is>
       </c>
     </row>
@@ -2893,14 +2937,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3756</v>
+        <v>0.3775</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2563</v>
+        <v>0.2576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3756 ± 0.2563</t>
+          <t>0.3775 ± 0.2576</t>
         </is>
       </c>
     </row>
@@ -2975,19 +3019,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7896</v>
+        <v>1.783</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7798</v>
+        <v>0.7846</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0625</v>
+        <v>2.0585</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2038</v>
+        <v>0.2081</v>
       </c>
       <c r="H2" t="n">
-        <v>125</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="3">
@@ -3005,19 +3049,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4008</v>
+        <v>1.3967</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4924</v>
+        <v>1.4871</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6628</v>
+        <v>1.6594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6139</v>
+        <v>0.6105</v>
       </c>
       <c r="H3" t="n">
-        <v>124</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="4">
@@ -3035,19 +3079,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4889</v>
+        <v>1.508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4647</v>
+        <v>1.486</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7539</v>
+        <v>1.7768</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3005</v>
+        <v>0.2989</v>
       </c>
       <c r="H4" t="n">
-        <v>132.2</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="5">
@@ -3095,19 +3139,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>30.0701</v>
+        <v>30.3556</v>
       </c>
       <c r="E6" t="n">
-        <v>9.9641</v>
+        <v>10.3112</v>
       </c>
       <c r="F6" t="n">
-        <v>30.138</v>
+        <v>30.4278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4474</v>
+        <v>0.4805</v>
       </c>
       <c r="H6" t="n">
-        <v>53.2</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="7">
@@ -3125,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>21.7634</v>
+        <v>21.7057</v>
       </c>
       <c r="E7" t="n">
-        <v>3.828</v>
+        <v>3.8056</v>
       </c>
       <c r="F7" t="n">
-        <v>21.967</v>
+        <v>21.9228</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4909</v>
+        <v>0.4914</v>
       </c>
       <c r="H7" t="n">
-        <v>62</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="8">
@@ -3155,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>44.4532</v>
+        <v>44.7435</v>
       </c>
       <c r="E8" t="n">
-        <v>28.2156</v>
+        <v>29.3701</v>
       </c>
       <c r="F8" t="n">
-        <v>50.8898</v>
+        <v>51.0304</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1822</v>
+        <v>0.2059</v>
       </c>
       <c r="H8" t="n">
-        <v>128.7</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="9">
@@ -3185,19 +3229,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>20.6511</v>
+        <v>20.6776</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3029</v>
+        <v>5.2958</v>
       </c>
       <c r="F9" t="n">
-        <v>22.38</v>
+        <v>22.4099</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4697</v>
+        <v>0.4713</v>
       </c>
       <c r="H9" t="n">
-        <v>128.2</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="10">
@@ -3212,22 +3256,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>16.9828</v>
+        <v>21.5423</v>
       </c>
       <c r="E10" t="n">
-        <v>4.7065</v>
+        <v>12.2585</v>
       </c>
       <c r="F10" t="n">
-        <v>17.9492</v>
+        <v>22.3912</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3028</v>
+        <v>0.2748</v>
       </c>
       <c r="H10" t="n">
-        <v>123.8</v>
+        <v>137.7</v>
       </c>
     </row>
   </sheetData>
